--- a/campanas.xlsx
+++ b/campanas.xlsx
@@ -1,33 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\COTIZADOR SOAT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74ABE71B-57A9-4388-B545-95AE4F0BF398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA2109D4-F665-4379-8287-27077DF355A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{99912D9F-99F3-46AE-B2B2-2B994E87127F}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{99912D9F-99F3-46AE-B2B2-2B994E87127F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -120,7 +111,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="40">
   <si>
     <t>ASEGURADORA</t>
   </si>
@@ -231,6 +222,15 @@
   </si>
   <si>
     <t>Todos</t>
+  </si>
+  <si>
+    <t>PANEL</t>
+  </si>
+  <si>
+    <t>TRANSPORTE PERSONAL</t>
+  </si>
+  <si>
+    <t>Campaña Uso Transporte Personal</t>
   </si>
 </sst>
 </file>
@@ -313,8 +313,12 @@
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
-      <top/>
-      <bottom/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -329,11 +333,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -654,13 +658,13 @@
   <cols>
     <col min="1" max="1" width="19.85546875" customWidth="1"/>
     <col min="2" max="2" width="24.5703125" customWidth="1"/>
-    <col min="3" max="3" width="28.85546875" customWidth="1"/>
+    <col min="3" max="3" width="31.7109375" customWidth="1"/>
     <col min="4" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="18.28515625" customWidth="1"/>
     <col min="7" max="7" width="24.140625" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
     <col min="9" max="9" width="15.85546875" customWidth="1"/>
-    <col min="10" max="10" width="28" customWidth="1"/>
+    <col min="10" max="10" width="36.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -717,10 +721,10 @@
       <c r="G2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="3">
         <v>45658</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="3">
         <v>46112</v>
       </c>
       <c r="J2" s="2" t="s">
@@ -749,10 +753,10 @@
       <c r="G3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="3">
         <v>45658</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="3">
         <v>45747</v>
       </c>
       <c r="J3" s="2" t="s">
@@ -781,10 +785,10 @@
       <c r="G4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="3">
         <v>45698</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="3">
         <v>45703</v>
       </c>
       <c r="J4" s="2" t="s">
@@ -813,10 +817,10 @@
       <c r="G5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="3">
         <v>46034</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="3">
         <v>46142</v>
       </c>
       <c r="J5" s="2" t="s">
@@ -845,10 +849,10 @@
       <c r="G6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="3">
         <v>46034</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="3">
         <v>46142</v>
       </c>
       <c r="J6" s="2" t="s">
@@ -863,7 +867,7 @@
         <v>36</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>27</v>
@@ -872,19 +876,19 @@
         <v>36</v>
       </c>
       <c r="F7" s="2">
-        <v>135</v>
+        <v>400</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="3">
         <v>46034</v>
       </c>
-      <c r="I7" s="4">
-        <v>46142</v>
+      <c r="I7" s="3">
+        <v>46387</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -895,7 +899,7 @@
         <v>36</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>29</v>
@@ -904,19 +908,19 @@
         <v>36</v>
       </c>
       <c r="F8" s="2">
-        <v>280</v>
+        <v>600</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="3">
         <v>46034</v>
       </c>
-      <c r="I8" s="4">
-        <v>46142</v>
+      <c r="I8" s="3">
+        <v>46387</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -927,7 +931,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>31</v>
@@ -936,19 +940,19 @@
         <v>36</v>
       </c>
       <c r="F9" s="2">
-        <v>280</v>
+        <v>700</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="3">
         <v>46034</v>
       </c>
-      <c r="I9" s="4">
-        <v>46142</v>
+      <c r="I9" s="3">
+        <v>46387</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -973,20 +977,47 @@
       <c r="G10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="3">
         <v>46054</v>
       </c>
-      <c r="I10" s="4">
-        <v>46112</v>
+      <c r="I10" s="3">
+        <v>46387</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
+    <row r="11" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="4">
+        <v>139</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="3">
+        <v>46053</v>
+      </c>
+      <c r="I11" s="3">
+        <v>46387</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
